--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:08</t>
+    <t xml:space="preserve">2026-09-17 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:04</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:54</t>
+    <t xml:space="preserve">2026-10-04 08:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2019_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:59</t>
+    <t xml:space="preserve">2026-10-05 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -609,7 +609,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>398784.62</v>
+        <v>398784.63</v>
       </c>
     </row>
     <row r="4">
@@ -1119,7 +1119,7 @@
         <v>2019</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>205309.62</v>
+        <v>205309.63</v>
       </c>
     </row>
     <row r="34">
